--- a/AAII_Financials/Quarterly/STT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>STT</t>
   </si>
@@ -656,273 +656,279 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4048000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3780000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3659000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3536000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3418000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3272000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3400000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3233000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3181000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3111000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3023000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2691000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3128000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3057000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1762000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1101000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>703000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>520000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>541000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>486000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>467000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>471000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>515000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>520000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>674000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>870000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>905000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1001000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1007000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1027000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>983000</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>916000</v>
       </c>
       <c r="AI8" s="3">
         <v>916000</v>
       </c>
       <c r="AJ8" s="3">
+        <v>916000</v>
+      </c>
+      <c r="AK8" s="3">
         <v>856000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>797000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>762000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>700000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>610000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>618000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>653000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1043,53 +1049,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4048000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3780000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3659000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3536000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3418000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3272000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3400000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3233000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3181000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3111000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3023000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2691000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3128000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3057000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1165,8 +1174,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1209,8 +1221,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1331,8 +1344,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1453,52 +1469,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>89000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>266000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>100000</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>97000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>188000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1575,82 +1594,85 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E15" s="3">
         <v>217000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>751000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>159000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>117000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>88000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>568000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>144000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>161000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>181000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>191000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>223000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>237000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>231000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-59000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-58000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-60000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-61000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>-62000</v>
       </c>
       <c r="V15" s="3">
         <v>-62000</v>
       </c>
       <c r="W15" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="X15" s="3">
         <v>-63000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-58000</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>-59000</v>
       </c>
       <c r="Z15" s="3">
         <v>-59000</v>
       </c>
       <c r="AA15" s="3">
-        <v>-58000</v>
+        <v>-59000</v>
       </c>
       <c r="AB15" s="3">
         <v>-58000</v>
@@ -1659,28 +1681,28 @@
         <v>-58000</v>
       </c>
       <c r="AD15" s="3">
-        <v>-59000</v>
+        <v>-58000</v>
       </c>
       <c r="AE15" s="3">
         <v>-59000</v>
       </c>
       <c r="AF15" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-60000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-81000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-47000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-48000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-50000</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>-54000</v>
       </c>
       <c r="AL15" s="3">
         <v>-54000</v>
@@ -1689,16 +1711,19 @@
         <v>-54000</v>
       </c>
       <c r="AN15" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="AO15" s="3">
         <v>-52000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-54000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-55000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,252 +1763,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2659000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2722000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2418000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2378000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2473000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2429000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2450000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2289000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2252000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2209000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2453000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2575000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2120000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2152000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2309000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>981000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>441000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>130000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-8000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-15000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>42000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>167000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>240000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>273000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>359000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>395000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>358000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>293000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>249000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>250000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>214000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>179000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>161000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>128000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>138000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>104000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>110000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1389000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1058000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1241000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1158000</v>
       </c>
-      <c r="G18" s="3">
-        <v>945000</v>
-      </c>
       <c r="H18" s="3">
+        <v>989000</v>
+      </c>
+      <c r="I18" s="3">
         <v>822000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1111000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>981000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>972000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>658000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>448000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>571000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>976000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>748000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>781000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>660000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>573000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>508000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>549000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>488000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>482000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>476000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>501000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>478000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>507000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>630000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>632000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>642000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>612000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>669000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>690000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>667000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>666000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>642000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>618000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>601000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>572000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>472000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>514000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>543000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2026,19 +2058,20 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>57000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>56000</v>
       </c>
       <c r="G20" s="3">
         <v>56000</v>
@@ -2046,23 +2079,23 @@
       <c r="H20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>54000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>56000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>60000</v>
       </c>
       <c r="L20" s="3">
         <v>60000</v>
       </c>
       <c r="M20" s="3">
+        <v>60000</v>
+      </c>
+      <c r="N20" s="3">
         <v>59000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>60000</v>
       </c>
       <c r="O20" s="3">
         <v>60000</v>
@@ -2071,207 +2104,213 @@
         <v>60000</v>
       </c>
       <c r="Q20" s="3">
+        <v>60000</v>
+      </c>
+      <c r="R20" s="3">
         <v>108000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>189000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>262000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>246000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>181000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>388000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>456000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>151000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>140000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>203000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>296000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>144000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>79000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>106000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-161000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>226000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>225000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>146000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>99000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>221000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>204000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>112000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-169000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1589000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1275000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1935000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1261000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1006000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1106000</v>
+      </c>
+      <c r="I21" s="3">
         <v>910000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1625000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1069000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1073000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>779000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>580000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>734000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1153000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>919000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1308000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1045000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1083000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1047000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1089000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1253000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1342000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1044000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1976000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>172000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1155000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1106000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1001000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1061000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1048000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>939000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>858000</v>
-      </c>
-      <c r="AH21" s="3">
-        <v>1180000</v>
       </c>
       <c r="AI21" s="3">
         <v>1180000</v>
       </c>
       <c r="AJ21" s="3">
+        <v>1180000</v>
+      </c>
+      <c r="AK21" s="3">
         <v>1086000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1006000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1097000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1033000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>848000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>604000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>846000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2314,8 +2353,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2392,252 +2431,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1389000</v>
+      </c>
+      <c r="E23" s="3">
         <v>969000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>918000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1102000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>889000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>822000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>960000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>925000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>912000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>598000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>201000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>511000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>916000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>688000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>889000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>849000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>835000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>754000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>730000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>876000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>938000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>627000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>641000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>681000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>803000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>774000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>638000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>721000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>718000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>635000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>529000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>893000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>891000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>788000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>717000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>822000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>776000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>584000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>345000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>636000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>305000</v>
+      </c>
+      <c r="E24" s="3">
         <v>205000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>171000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>241000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>196000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>178000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>177000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>195000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>201000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>135000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>89000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>153000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>139000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>156000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>159000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>88000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>150000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>33000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>162000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>175000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>108000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>104000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>126000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>109000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>140000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>74000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>138000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>131000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>127000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>124000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>129000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>129000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>90000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>137000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>156000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>82000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-248000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>72000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2758,252 +2806,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1084000</v>
+      </c>
+      <c r="E26" s="3">
         <v>764000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>747000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>861000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>693000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>644000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>783000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>730000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>711000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>463000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>210000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>422000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>763000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>549000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>733000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>690000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>747000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>604000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>697000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>714000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>763000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>519000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>537000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>555000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>694000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>634000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>564000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>583000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>587000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>508000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>405000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>764000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>733000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>659000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>627000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>685000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>620000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>502000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>593000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1026000</v>
+      </c>
+      <c r="E27" s="3">
         <v>705000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>688000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>802000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>630000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>597000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>728000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>682000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>655000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>418000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>172000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>398000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>726000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>525000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>696000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>669000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>712000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>583000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>662000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>693000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>728000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>489000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>498000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>517000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>662000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>580000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>492000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>528000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>537000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>452000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>364000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>708000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>697000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>603000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>591000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>629000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>584000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>446000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>557000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3124,8 +3181,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3198,8 +3258,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -3216,24 +3276,24 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>32000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-257000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3246,8 +3306,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3368,8 +3431,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3490,19 +3556,22 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>-57000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-56000</v>
       </c>
       <c r="G32" s="3">
         <v>-56000</v>
@@ -3510,23 +3579,23 @@
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>-54000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-56000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-60000</v>
       </c>
       <c r="L32" s="3">
         <v>-60000</v>
       </c>
       <c r="M32" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="N32" s="3">
         <v>-59000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-60000</v>
       </c>
       <c r="O32" s="3">
         <v>-60000</v>
@@ -3535,207 +3604,213 @@
         <v>-60000</v>
       </c>
       <c r="Q32" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="R32" s="3">
         <v>-108000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-189000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-262000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-246000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-181000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-388000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-456000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-151000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-140000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-203000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-296000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-144000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-79000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-106000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>34000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>161000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-226000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-225000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-146000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-99000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-221000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-204000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-112000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>169000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-93000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1084000</v>
+      </c>
+      <c r="E33" s="3">
         <v>764000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>747000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>861000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>693000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>644000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>783000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>730000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>711000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>463000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>210000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>422000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>763000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>549000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>696000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>669000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>712000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>583000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>662000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>693000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>728000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>489000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>498000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>517000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>662000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>580000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>492000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>528000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>537000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>452000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>396000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>708000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>697000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>603000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>334000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>629000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>584000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>446000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>557000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3856,257 +3931,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1084000</v>
+      </c>
+      <c r="E35" s="3">
         <v>764000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>747000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>861000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>693000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>644000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>783000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>730000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>711000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>463000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>210000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>422000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>763000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>549000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>696000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>669000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>712000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>583000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>662000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>693000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>728000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>489000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>498000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>517000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>662000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>580000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>492000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>528000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>537000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>452000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>396000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>708000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>697000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>603000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>334000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>629000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>584000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>446000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>557000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4149,8 +4233,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4193,297 +4278,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4290000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6518000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4433000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4756000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4020000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4658000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3145000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4067000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2898000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3413000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4047000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4009000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3930000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3698000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3970000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2748000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3515000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2976000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3631000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4606000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4619000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4552000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3467000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4848000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3685000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4932000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3302000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3598000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3742000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4469000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3597000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4145000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3886000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2546000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2107000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3939000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3156000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2909000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1314000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3490000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>163920000</v>
+      </c>
+      <c r="E42" s="3">
         <v>141094000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>138724000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>134810000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>137376000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>135438000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>131587000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>118612000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>112871000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>138672000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>100437000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>87101000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>94859000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>94425000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>131611000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>129267000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>124961000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>136461000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>136536000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>145328000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>150603000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>146521000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>145015000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>100907000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>112914000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>171942000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>94643000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>93913000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>93515000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>84349000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>103343000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>97268000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>110049000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>110641000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>94978000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>93896000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>94344000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>95484000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>102440000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>110556000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4856000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4907000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4387000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4361000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4270000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1283000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3728000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3858000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3591000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3890000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3577000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3580000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3392000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3399000</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4559,8 +4651,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4603,8 +4698,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4681,53 +4776,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8180000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5042000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4160000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4799000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6940000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9492000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5267000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6357000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5798000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4874000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6301000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5804000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5320000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4575000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4803,53 +4901,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>182421000</v>
+      </c>
+      <c r="E46" s="3">
         <v>158522000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>152541000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>149665000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>153472000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>151744000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>144465000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>133733000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>125946000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>151674000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>114960000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>101104000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>108172000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>106776000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4925,374 +5026,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>111684000</v>
+      </c>
+      <c r="E47" s="3">
         <v>112256000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>109078000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>113720000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>117231000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>116373000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>109939000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>110723000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>110849000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>104543000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>104624000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>106342000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>109461000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>110893000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3245000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3250000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3256000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3236000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3162000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3140000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3214000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3027000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3095000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3186000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2696000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2837000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2899000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3064000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2597000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2668000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2882000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2797000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2791000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2718000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2259000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2099000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2115000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2088000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2363000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4674000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4146000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4039000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3944000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3817000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3610000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3533000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3486000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3375000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3310000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3204000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3157000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2928000</v>
-      </c>
-      <c r="P48" s="3">
-        <v>2815000</v>
       </c>
       <c r="Q48" s="3">
         <v>2815000</v>
       </c>
       <c r="R48" s="3">
+        <v>2815000</v>
+      </c>
+      <c r="S48" s="3">
         <v>2761000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2741000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2775000</v>
-      </c>
-      <c r="U48" s="3">
-        <v>2803000</v>
       </c>
       <c r="V48" s="3">
         <v>2803000</v>
       </c>
       <c r="W48" s="3">
+        <v>2803000</v>
+      </c>
+      <c r="X48" s="3">
         <v>2791000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2775000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2874000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2982000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3014000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3040000</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>3140000</v>
       </c>
       <c r="AD48" s="3">
         <v>3140000</v>
       </c>
       <c r="AE48" s="3">
+        <v>3140000</v>
+      </c>
+      <c r="AF48" s="3">
         <v>3120000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3129000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2214000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2193000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2189000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2194000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2186000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2167000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2137000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2101000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2062000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2042000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8922000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8993000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9094000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8874000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8932000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8809000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8780000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8999000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8960000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8840000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8931000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8850000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8979000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9023000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9039000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8919000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9119000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9326000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9437000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9537000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9562000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9636000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9510000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9477000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9452000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9469000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9586000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9577000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9720000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>9757000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9815000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7477000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7473000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7646000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7635000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7655000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>7638000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>7565000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>7564000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>7760000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5413,8 +5526,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5535,130 +5651,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>56949000</v>
+      </c>
+      <c r="E52" s="3">
         <v>57398000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>44079000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>47749000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>45474000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>47002000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>42796000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38973000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>36273000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30149000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28009000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28625000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29879000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26519000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1127000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1083000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1027000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>775000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>254000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>196000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>212000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>221000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>233000</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>199000</v>
       </c>
       <c r="AA52" s="3">
         <v>199000</v>
       </c>
       <c r="AB52" s="3">
+        <v>199000</v>
+      </c>
+      <c r="AC52" s="3">
         <v>206000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>216000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>95000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>101000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>100000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>113000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>120000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>107000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>113000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>213000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>211000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>214000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>210000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>215000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5779,130 +5901,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>418381000</v>
+      </c>
+      <c r="E54" s="3">
         <v>392165000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>366047000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>371070000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>376717000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>372693000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>353240000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>338481000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>325603000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>338003000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>297258000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>284415000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>294561000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>290816000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>301450000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>303568000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>300223000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>322350000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>314624000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>323139000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>326528000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>316885000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>314706000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>272075000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>280242000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>362527000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>245610000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>244606000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>241540000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>228332000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>244596000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>234007000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>248308000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>250286000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>238425000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>235986000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>238274000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>236802000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>242698000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>256140000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5945,8 +6073,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5989,53 +6118,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>319547000</v>
+      </c>
+      <c r="E57" s="3">
         <v>293341000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>274350000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>279999000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>283024000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>272056000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>261920000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>247429000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>239160000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>251884000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>220970000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>213001000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>222316000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>223631000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6111,53 +6241,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>31736000</v>
+      </c>
+      <c r="E58" s="3">
         <v>35131000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>33912000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>29518000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>27668000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>39896000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>35732000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>33658000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>33342000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>32115000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>26127000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8387000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>23195000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18469000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6188,53 +6321,56 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>1982000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8413000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6789000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2398000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
       <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
         <v>3986000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>5120000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>5321000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>5180000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>5985000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>5777000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6277,131 +6413,134 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>22525000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21326000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17989000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>26866000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17048000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22288000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23067000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>31722000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>27503000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>22064000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>23634000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>22365000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>18398000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>23734000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>22355000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>23196000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18989000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>23500000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>19170000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18423000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9724000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>12678000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>11280000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>11413000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>10899000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>14020000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>364274000</v>
+      </c>
+      <c r="E60" s="3">
         <v>339049000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>316106000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>318609000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>323336000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>321019000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>305763000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>291608000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>280955000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>293689000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>255438000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>242095000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>253029000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>249623000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6477,135 +6616,141 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25704000</v>
+      </c>
+      <c r="E61" s="3">
         <v>25233000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>21951000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24688000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25911000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24846000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21987000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20902000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19737000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19746000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17862000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18564000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>17178000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16305000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14996000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13999000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13530000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13922000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13475000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12978000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13032000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>13836000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13805000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13853000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15587000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15538000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>12468000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11445000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11353000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11151000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11093000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10335000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10387000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10944000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11620000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>11716000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11737000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>11394000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>11430000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>11834000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3">
+        <v>12000</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>5</v>
@@ -6643,8 +6788,8 @@
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -6721,8 +6866,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6843,8 +6991,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6965,8 +7116,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7087,130 +7241,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>390113000</v>
+      </c>
+      <c r="E66" s="3">
         <v>364423000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>338206000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>343428000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>349410000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>346001000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>327914000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>312653000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>300841000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>313570000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>273459000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>260794000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>270357000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>266066000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>276259000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>277920000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>274456000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>296126000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>287261000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>295825000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>301361000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>291880000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>288506000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>246517000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>255369000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>338666000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>221179000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>219397000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>216086000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>203294000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>219859000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>209454000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>225737000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>227887000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>216108000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>213489000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>216206000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>215508000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>221479000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>233990000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7253,8 +7413,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7375,8 +7536,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7497,8 +7661,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7518,19 +7685,19 @@
         <v>3559000</v>
       </c>
       <c r="I70" s="3">
-        <v>2816000</v>
+        <v>3559000</v>
       </c>
       <c r="J70" s="3">
         <v>2816000</v>
       </c>
       <c r="K70" s="3">
-        <v>2468000</v>
+        <v>2816000</v>
       </c>
       <c r="L70" s="3">
         <v>2468000</v>
       </c>
       <c r="M70" s="3">
-        <v>1976000</v>
+        <v>2468000</v>
       </c>
       <c r="N70" s="3">
         <v>1976000</v>
@@ -7566,7 +7733,7 @@
         <v>1976000</v>
       </c>
       <c r="Y70" s="3">
-        <v>2471000</v>
+        <v>1976000</v>
       </c>
       <c r="Z70" s="3">
         <v>2471000</v>
@@ -7578,10 +7745,10 @@
         <v>2471000</v>
       </c>
       <c r="AC70" s="3">
+        <v>2471000</v>
+      </c>
+      <c r="AD70" s="3">
         <v>2962000</v>
-      </c>
-      <c r="AD70" s="3">
-        <v>3690000</v>
       </c>
       <c r="AE70" s="3">
         <v>3690000</v>
@@ -7596,7 +7763,7 @@
         <v>3690000</v>
       </c>
       <c r="AI70" s="3">
-        <v>3196000</v>
+        <v>3690000</v>
       </c>
       <c r="AJ70" s="3">
         <v>3196000</v>
@@ -7619,8 +7786,11 @@
       <c r="AP70" s="3">
         <v>3196000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>3196000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7741,130 +7911,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32660000</v>
+      </c>
+      <c r="E72" s="3">
         <v>31864000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>31392000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30938000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>30373000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29959000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29582000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29073000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28615000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28166000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27957000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27993000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>27808000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>27342000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>27028000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>26552000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>26115000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>25612000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>25238000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>24785000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>24300000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>23751000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>23442000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>23128000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>22794000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22315000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21918000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21612000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21274000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>20911000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>20553000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>20387000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>19856000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>19311000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>18856000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>18675000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>18202000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>17762000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>17459000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>17047000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7985,8 +8161,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8107,8 +8286,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8229,130 +8411,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24709000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24183000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24282000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24083000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23748000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23133000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22510000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23012000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22294000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21965000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21823000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21645000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22228000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22774000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23215000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>23672000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23791000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24248000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25387000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>25338000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23191000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>23029000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23729000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>23087000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>22402000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>21390000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>21469000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21519000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>21764000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>21348000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>21047000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20863000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>19375000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>19203000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>19121000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>19301000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>18872000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>18098000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>18023000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>18954000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8473,257 +8661,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1084000</v>
+      </c>
+      <c r="E81" s="3">
         <v>764000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>747000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>861000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>693000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>644000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>783000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>730000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>711000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>463000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>210000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>422000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>763000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>549000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>696000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>669000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>712000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>583000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>662000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>693000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>728000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>489000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>498000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>517000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>662000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>580000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>492000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>528000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>537000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>452000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>396000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>708000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>697000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>603000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>334000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>629000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>584000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>446000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>557000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8766,130 +8963,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E83" s="3">
         <v>34000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>514000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>88000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>101000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>121000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>132000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>163000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>177000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>171000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>360000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>138000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>188000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>232000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>419000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>196000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>248000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>293000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>359000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>377000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>404000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>417000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1335000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>-509000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>352000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>332000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>363000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>340000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>330000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>304000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>329000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>287000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>289000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>298000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>289000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>275000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>257000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>264000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>259000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>210000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9010,8 +9211,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9132,8 +9336,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9254,8 +9461,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9376,8 +9586,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9498,130 +9711,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2326000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12143000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10042000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7901000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8441000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2396000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7430000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2708000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7644000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-844000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4182000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>222000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-852000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2862000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7036000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4467000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4135000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4586000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4227000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>388000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7593000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3732000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3376000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5219000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1336000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4039000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1053000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4717000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>415000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-495000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1396000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5659000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1434000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4836000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>5076000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-2142000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>490000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3509000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>14000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-2736000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9664,130 +9883,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-675000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-270000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-267000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-243000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-319000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-226000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-249000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-234000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-213000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-230000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-329000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-135000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-170000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-182000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-204000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-210000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-182000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-138000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-255000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-197000</v>
       </c>
       <c r="W91" s="3">
         <v>-197000</v>
       </c>
       <c r="X91" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-162000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-136000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-153000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-157000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-114000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-161000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-227000</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-171000</v>
       </c>
       <c r="AF91" s="3">
         <v>-171000</v>
       </c>
       <c r="AG91" s="3">
+        <v>-171000</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-173000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-151000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-138000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-147000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-152000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-161000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-164000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-149000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9908,8 +10131,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10030,130 +10256,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-25786000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4383000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1943000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>57000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-384000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14607000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11042000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6267000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>19178000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-41352000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13828000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>10168000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2086000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>14312000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1095000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5335000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>17582000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4336000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1694000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2610000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9892000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>6804000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-39412000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>12173000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>74478000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-112773000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5523000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5656000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-13118000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>21671000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-15927000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>13163000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>7241000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-8973000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-10831000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>5863000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>1806000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>3210000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>9782000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-3266000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10196,8 +10428,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10240,86 +10473,89 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>-232000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-209000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-210000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-209000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-208000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-179000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-181000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-184000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-185000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-183000</v>
       </c>
       <c r="AA96" s="3">
         <v>-183000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-186000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-189000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-175000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-179000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-178000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-154000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-189000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-210000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-191000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-198000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-178000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-201000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-182000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-188000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10440,8 +10676,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10562,8 +10801,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10684,130 +10926,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>25884000</v>
+      </c>
+      <c r="E100" s="3">
         <v>18611000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12308000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7222000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8187000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>13724000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>17550000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4728000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12049000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>41562000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9684000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10311000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1002000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11722000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4719000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>101000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12908000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-905000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3508000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3011000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>17552000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1987000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>34655000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5791000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-77061000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>110364000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4174000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1180000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>11976000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-20304000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>13746000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-18326000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4467000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>4576000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>3923000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2938000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2049000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-5124000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-11972000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>4819000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10850,8 +11098,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10928,126 +11176,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2228000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2085000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-323000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>736000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-638000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1513000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-922000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1169000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-515000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-634000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>38000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>79000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>232000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-272000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1222000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-767000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>539000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-655000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-975000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>67000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1085000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1381000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1163000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1247000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1630000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-296000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>241000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-727000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>872000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-785000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>496000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1340000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>439000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1832000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>783000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>247000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1595000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-2176000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1183000</v>
       </c>
     </row>
